--- a/astro-site/public/dl/pastry-shop-checklist-templates/02-pastry-kitchen-production-checklists.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/02-pastry-kitchen-production-checklists.xlsx
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Score with a lame before baking</t>
+          <t>Score with a lame before baking; sesame and seed toppings go on their own sheet pans and bench (allergen cross-contact)</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Make sablee dough (softened butter + sugar + flour)</t>
+          <t>Make sablée dough (softened butter + sugar + flour)</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Make brisee dough for quiches / savory tarts</t>
+          <t>Make brisée dough for quiches / savory tarts</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Syrup at 244–250 °F · butter at 64–68 °F</t>
+          <t>Italian: syrup at 244–250 °F · Swiss: whites and sugar to 160 °F · butter at 64–68 °F</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Make chocolate mousse (tempered chocolate + cream + cooked Italian or Swiss meringue or pasteurized whites, FDA Food Code 3-302.13)</t>
+          <t>Make chocolate mousse (melted chocolate + cream + cooked Italian or Swiss meringue or pasteurized whites, FDA Food Code 3-302.13)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Make pralines and nut praline</t>
+          <t>Make praline paste and nut brittle on the nut station: dedicated scoops, sifter and bowls, cleaned before the next product (allergen cross-contact)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Stock the viennoiserie case (croissants, pain au chocolat, custard danishes)</t>
+          <t>Stock the viennoiserie case (croissants, pain au chocolat, palmiers, fruit danishes)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Ambient · restock in small batches</t>
+          <t>Ambient · restock in small batches · custard-, cream- or cheese-filled pieces go in the refrigerated case at 41 °F or below (FDA Food Code 3-501.16)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
